--- a/template_bukti_dukung/INDIKATOR_01_TATA_KELOLA/Template_Matriks_Penyelarasan_Arsitektur_SIA_SPBE_Indikator01.xlsx
+++ b/template_bukti_dukung/INDIKATOR_01_TATA_KELOLA/Template_Matriks_Penyelarasan_Arsitektur_SIA_SPBE_Indikator01.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriks Bukti Dukung" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_SIA_SPBE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriks_Penyelarasan_6_Domain" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peta_Rencana_Program_5_Tahun" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kamus_Referensi_SIA_Nasional" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,27 +31,97 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001E3A8A"/>
+      <color rgb="001F4E79"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00555555"/>
+      <color rgb="00595959"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00274E13"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="004C1130"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000C343D"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000B5394"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E4620"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -57,8 +130,68 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
+        <fgColor rgb="00F2F4F7"/>
+        <bgColor rgb="00F2F4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+        <bgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C3D9FF"/>
+        <bgColor rgb="00C3D9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD1DC"/>
+        <bgColor rgb="00EAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E0E3"/>
+        <bgColor rgb="00D0E0E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+        <bgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+        <bgColor rgb="007030A0"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,38 +205,93 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D3D3D3"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00D3D3D3"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D3D3D3"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D3D3D3"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -470,285 +658,1474 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="94" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MATRIKS PENYELARASAN 6 DOMAIN ARSITEKTUR PEMDI DENGAN SIA-SPBE NASIONAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+          <t>DASHBOARD KETERPADUAN ARSITEKTUR SPBE KE PLATFORM SIA-SPBE NASIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Evaluasi Kematangan Tata Kelola Pemerintah Digital - PermenPANRB No. 8/2026</t>
+          <t>Kertas Kerja Bukti Evaluasi Indikator 1 PermenPANRB No. 8/2026 (Level 4 - Terpadu Nasional)</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="28" customHeight="1">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Status Akun SIA-SPBE</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Penyelarasan 6 Domain</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Total Entitas Terpetakan</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Integrasi ke DPA/Renja</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Validasi KemenPANRB</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Target Kematangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TERVALIDASI</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>100% Tuntas</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>248 Komponen</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Tersinkronisasi</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>DISETUJUI RESMI</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Level 4 (Terpadu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>STATUS VALIDASI KETERPADUAN 6 DOMAIN ARSITEKTUR INSTANSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Kode Domain</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Nama Domain Arsitektur</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Komponen Instansi</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Jumlah Objek Terdata</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Kode Referensi SIA Nasional</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Status Sinkronisasi</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Tanggal Verifikasi KemenPANRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Domain Proses Bisnis (Peta Probis Level 0-2)</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Rab - Referensi Arsitektur Bisnis</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Tersinkronisasi 100%</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Domain Data &amp; Informasi (Katalog Data SDI)</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>76</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Rad - Referensi Arsitektur Data</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Tersinkronisasi 100%</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Domain Layanan Digital (Katalog Layanan Publik/Gov)</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Ral - Referensi Arsitektur Layanan</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Tersinkronisasi 100%</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Domain Aplikasi (Aplikasi Berbagi Pakai &amp; Khusus)</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Raa - Referensi Arsitektur Aplikasi</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>Tersinkronisasi 100%</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Domain Infrastruktur (Data Center, JIP, Cloud PDN)</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Rai - Referensi Arsitektur Infrastruktur</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Tersinkronisasi 100%</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Domain Keamanan Informasi (SMKI, CSIRT, TTE)</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Rak - Referensi Arsitektur Keamanan</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>Tersinkronisasi 100%</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="89" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="53" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>MATRIKS PEMETAAN ENTITAS ARSITEKTUR INSTANSI KE REFERENSI ARSITEKTUR SIA-SPBE NASIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>No Entitas</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>Kode Komponen Instansi</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>Nama Objek / Sistem Instansi</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>Kode Referensi SIA-SPBE</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status Validasi KemenPANRB</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Unit Kerja PIC</t>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>Deskripsi Referensi Nasional KemenPANRB</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>OPD Pengampu / Penanggung Jawab</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>Keterpaduan API / Interkoneksi</t>
+        </is>
+      </c>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Status Validasi Nasional</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>ENT-PB-01</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Probis</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>PROBIS.01.02.04</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Layanan Perizinan Berusaha Terpadu Satu Pintu</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Rab.02.01</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Penyelenggaraan Perizinan &amp; Non-Perizinan Daerah</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>DPMPTSP</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Terintegrasi OSS RBA</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>VALID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>D.01</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Domain Proses Bisnis</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Peta Tematik Layanan Administrasi &amp; Publik</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>REF-PB-2026-001</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Tervalidasi (Approved)</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Biro Organisasi / Bagian Ortala</t>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>ENT-PB-02</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Probis</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>PROBIS.02.01.01</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Pengelolaan Naskah Dinas Elektronik Instansi</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Rab.01.03</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Penyelenggaraan Administrasi Persuratan Pemerintah</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>Diskominfo / Bag. Umum</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>Terintegrasi SRIKANDI</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>VALID</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>D.02</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Domain Data &amp; Informasi</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Katalog Standar Data &amp; Metadata Sektoral</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>REF-DT-2026-012</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Tervalidasi (Approved)</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Bappeda / Diskominfo</t>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>ENT-DATA-01</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>DATA.03.01.002</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Basis Data Tunggal Profil Kependudukan Terpadu</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Rad.01.01</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Data Induk Kependudukan dan Catatan Sipil</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Disdukcapil</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>API SIAK Terpusat Kemendagri</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>VALID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>D.03</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Domain Aplikasi SPBE</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Katalog Aplikasi Khusus dan Umum Instansi</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>REF-AP-2026-045</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Tervalidasi (Approved)</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Diskominfo (Bidang Aptika)</t>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>ENT-DATA-02</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>DATA.04.02.005</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Data Geospasial RTRW dan Tematik Tata Ruang</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Rad.02.04</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Data Geospasial Informasi Geospasial Tematik</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>Bappeda / Dinas PUPR</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>Node JIGN BIG Nasional</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>VALID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>D.04</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Domain Infrastruktur</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>ENT-LAY-01</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Layanan</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>LAY.01.001</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Portal Pelayanan Warga Satu Pintu (SuperApp)</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Ral.01.02</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Layanan Portal Pelayanan Publik Terpadu</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Diskominfo</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>SSO Digital ID ASN/Warga</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>ENT-LAY-02</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Layanan</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>LAY.02.004</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Layanan Cuti Online dan Kinerja Pegawai ASN</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Ral.02.03</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Layanan Administrasi Manajemen ASN</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>BKPSDM</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>API Dua Arah SIASN BKN</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>ENT-APP-01</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Aplikasi</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>APP.02.001</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Sistem Informasi Manajemen Kepegawaian (SIMPEG)</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Raa.02.01</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Aplikasi Manajemen Kepegawaian Daerah</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>BKPSDM</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>Microservices Cloud Ready</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>ENT-APP-02</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Aplikasi</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>APP.03.004</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Sistem Pajak &amp; Retribusi Daerah Online (e-PBB/BPHTB)</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Raa.01.04</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Aplikasi Pengelolaan Pendapatan Asli Daerah</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Bapenda</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>Gateway Bank BPD / QRIS</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>ENT-INFRA-01</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Infrastruktur</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>INF.01.001</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Infrastruktur Cloud Tenant Pusat Data Nasional</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Rai.01.01</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Komputasi Cloud Pemerintah PDN Nasional</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Diskominfo</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>Virtual Data Center PDN</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>ENT-SEC-01</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Keamanan</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>SEC.01.001</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Pusat Operasi Tanggap Insiden Siber (CSIRT Instansi)</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Rak.01.02</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Penanganan Insiden Siber dan Keamanan Informasi</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>Diskominfo / CSIRT</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>Gov-CSIRT BSSN Terkoneksi</t>
+        </is>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="99" customWidth="1" min="1" max="1"/>
+    <col width="67" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>ROADMAP PETA RENCANA INISIATIF STRATEGIS PEMERINTAH DIGITAL (2026-2030) &amp; SINKRONISASI RENJA/DPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>No Inisiatif</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Nama Program / Inisiatif Strategis</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Keterkaitan 6 Domain</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Target Layanan yang Dihasilkan</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>OPD Penanggung Jawab</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Tahapan 2026</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Tahapan 2027-2028</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Tahapan 2029-2030</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="inlineStr">
+        <is>
+          <t>Kode Rekening Program DPA</t>
+        </is>
+      </c>
+      <c r="J3" s="20" t="inlineStr">
+        <is>
+          <t>Estimasi Alokasi (Rp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>INIT-01</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Penyatuan Portal Layanan Publik Daerah Terpadu (SuperApp)</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Layanan &amp; Aplikasi</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>1 Portal terpadu menggantikan 24 web terpisah</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Diskominfo</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>Integrasi 8 Layanan Utama</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>Ekspansi Layanan Perizinan</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>AI Chatbot &amp; INAGov SSO</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>2.16.03.2.01.0004</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t>Rp 850.000.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>INIT-02</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Implementasi Satu Data Indonesia &amp; Geoportal Tematik</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>Data &amp; Probis</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>Data warehouse terpusat &amp; metadata tervalidasi</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>Bappeda &amp; Diskominfo</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>Katalog Data 100% OPD</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>Integrasi SPLP Nasional</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>Pemanfaatan Big Data Analytics</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>2.16.02.2.01.0002</t>
+        </is>
+      </c>
+      <c r="J5" s="26" t="inlineStr">
+        <is>
+          <t>Rp 650.000.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>INIT-03</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Migrasi Menyeluruh Server OPD ke Cloud Pusat Data Nasional (PDN)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Infrastruktur</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Efisiensi 100% server fisik lokal menuju PDN Komdigi</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Diskominfo</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Migrasi 30 Aplikasi Strategis</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>Decommissioning Server Lama</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>Multi-AZ Cloud Resilience</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>2.16.03.2.02.0001</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>Rp 1.200.000.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>INIT-04</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Penguatan CSIRT Daerah &amp; Sertifikasi ISO 27001 SMKI</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>Keamanan Informasi</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>Kesiapsiagaan insiden siber &amp; registrasi STR BSSN</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>Diskominfo (CSIRT)</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>Pelaksanaan Cyber Drill &amp; PIR</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>Audit Eksternal ISO 27001</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>Zero Trust Architecture</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>2.16.03.2.03.0005</t>
+        </is>
+      </c>
+      <c r="J7" s="26" t="inlineStr">
+        <is>
+          <t>Rp 480.000.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>INIT-05</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Digitalisasi Naskah Dinas Terpadu SRIKANDI &amp; TTE BSrE 100%</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Layanan Administrasi</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Arsip digital 100% paperless seluruh unit kerja</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Dinas Perpustakaan &amp; Kominfo</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>Pemberlakuan TTE 100% SK</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Penghapusan Berkas Manual</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>Integrasi Arsip Statis ANRI</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>2.16.01.2.01.0003</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>Rp 320.000.000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="66" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>KAMUS KODE REFERENSI ARSITEKTUR SPBE NASIONAL KEMENTERIAN PANRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Kode Klasifikasi</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Kategori Referensi Nasional</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Nama Nomenklatur Standar</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Regulasi Acuan Nasional</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Keterangan Integrasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Rab.01</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Referensi Arsitektur Bisnis</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Penyelenggaraan Manajemen Pemerintahan Umum</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Perpres 95/2018</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Wajib digunakan untuk Probis Manajemen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Rab.02</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Referensi Arsitektur Bisnis</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Penyelenggaraan Pelayanan Publik Sektoral</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>UU 25/2009</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Wajib digunakan untuk Probis Pelayanan Warga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Rad.01</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Referensi Arsitektur Data</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Data Referensi dan Data Induk Nasional</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Perpres 39/2019</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Standar Pengkodean Master Data Kependudukan &amp; ASN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Rad.02</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Referensi Arsitektur Data</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Data Transaksi Elektronik &amp; Geospasial</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Perpres 27/2014</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>Standar Simpul Jaringan Geoportal BIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Ral.01</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Referensi Arsitektur Layanan</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Layanan Publik Berbasis Elektronik Terpadu</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>PermenPANRB 8/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Katalog Standar Layanan Publik Pemerintah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Raa.01</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Referensi Arsitektur Aplikasi</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Aplikasi Umum Berbagi Pakai Nasional</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Perpres 132/2022</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>Prioritas Penggunaan Aplikasi Nasional Bebas Duplikasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Rai.01</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Referensi Arsitektur Infrastruktur</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Pusat Data Nasional &amp; Jaringan Intra Pemerintah</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>REF-INF-2026-003</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Tervalidasi (Approved)</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Diskominfo (Bidang IKP/Jaringan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>D.05</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Domain Keamanan</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Sistem Manajemen Keamanan Informasi &amp; CSIRT</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>REF-SEC-2026-009</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Tervalidasi (Approved)</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Diskominfo (Sandi &amp; Siber)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>D.06</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Domain Layanan Digital</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Portal Pelayanan Publik &amp; Administrasi Terpadu</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>REF-LAY-2026-021</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Tervalidasi (Approved)</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>DPMPTSP / Seluruh OPD</t>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Perpres 95/2018</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Standardisasi Komputasi Awan dan Interkoneksi Fiber Optik</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Rak.01</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Referensi Arsitektur Keamanan</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Kerangka Pengamanan Informasi SPBE &amp; CSIRT</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Peraturan BSSN 10/2020</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Standar Kriptografi TTE dan Manajemen Kerentanan</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>